--- a/data/reference/Сводная информация_объединённая.xlsx
+++ b/data/reference/Сводная информация_объединённая.xlsx
@@ -819,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:P66"/>
+  <dimension ref="A3:P65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col width="7.26953125" customWidth="1" style="1" min="1" max="1"/>
@@ -3389,1174 +3389,1116 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>Кустовое</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="n">
-        <v>3245</v>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
-        <is>
-          <t>Соли</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>45892</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>45959</v>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>Новая выборка — 67 дней</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>45939.30069444444</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>45959</v>
-      </c>
-      <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
-      <c r="L46" s="13">
-        <f>M46/N46</f>
-        <v/>
-      </c>
-      <c r="M46" s="3">
-        <f>I46-H46</f>
-        <v/>
-      </c>
-      <c r="N46" s="27">
-        <f>F46-E46</f>
-        <v/>
-      </c>
-      <c r="O46" s="29" t="inlineStr">
-        <is>
-          <t>новая</t>
-        </is>
-      </c>
-      <c r="P46" s="32" t="inlineStr">
-        <is>
-          <t>47-3245.xlsx</t>
+      <c r="A46" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="n">
+        <v>1151</v>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>46137.08333333334</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>46149.08333333334</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="11" t="n"/>
+      <c r="K46" s="11" t="n"/>
+      <c r="L46" s="14">
+        <f>M47/N47</f>
+        <v/>
+      </c>
+      <c r="M46" s="4">
+        <f>I47-H47</f>
+        <v/>
+      </c>
+      <c r="N46" s="26">
+        <f>F47-E47</f>
+        <v/>
+      </c>
+      <c r="O46" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P46" s="33" t="inlineStr">
+        <is>
+          <t>1151_ЮЯ_Нормальная работа.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="A47" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>Южно-Ягунское</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n">
-        <v>1151</v>
-      </c>
-      <c r="D47" s="22" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>1213л</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
         <is>
           <t>Нормальная работа</t>
         </is>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="12" t="n">
+        <v>46125.08333333334</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="n"/>
+      <c r="I47" s="12" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="12" t="n"/>
+      <c r="L47" s="13">
+        <f>M48/N48</f>
+        <v/>
+      </c>
+      <c r="M47" s="3">
+        <f>I48-H48</f>
+        <v/>
+      </c>
+      <c r="N47" s="27">
+        <f>F48-E48</f>
+        <v/>
+      </c>
+      <c r="O47" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P47" s="32" t="inlineStr">
+        <is>
+          <t>1213л_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>1214у</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="11" t="n"/>
+      <c r="K48" s="11" t="n"/>
+      <c r="L48" s="14">
+        <f>M49/N49</f>
+        <v/>
+      </c>
+      <c r="M48" s="4">
+        <f>I49-H49</f>
+        <v/>
+      </c>
+      <c r="N48" s="26">
+        <f>F49-E49</f>
+        <v/>
+      </c>
+      <c r="O48" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P48" s="33" t="inlineStr">
+        <is>
+          <t>1214у_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>46129.08333333334</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>46149.08333333334</v>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="n"/>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="13">
+        <f>M50/N50</f>
+        <v/>
+      </c>
+      <c r="M49" s="3">
+        <f>I50-H50</f>
+        <v/>
+      </c>
+      <c r="N49" s="27">
+        <f>F50-E50</f>
+        <v/>
+      </c>
+      <c r="O49" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P49" s="32" t="inlineStr">
+        <is>
+          <t>1247_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>46129.08333333334</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="11" t="n"/>
+      <c r="K50" s="11" t="n"/>
+      <c r="L50" s="14">
+        <f>M51/N51</f>
+        <v/>
+      </c>
+      <c r="M50" s="4">
+        <f>I51-H51</f>
+        <v/>
+      </c>
+      <c r="N50" s="26">
+        <f>F51-E51</f>
+        <v/>
+      </c>
+      <c r="O50" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P50" s="33" t="inlineStr">
+        <is>
+          <t>126_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>129л</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>46125.08333333334</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>46149.08333333334</v>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="n"/>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="13">
+        <f>M52/N52</f>
+        <v/>
+      </c>
+      <c r="M51" s="3">
+        <f>I52-H52</f>
+        <v/>
+      </c>
+      <c r="N51" s="27">
+        <f>F52-E52</f>
+        <v/>
+      </c>
+      <c r="O51" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P51" s="32" t="inlineStr">
+        <is>
+          <t>129л_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>1396у</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>46113.08333333334</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>46143.08333333334</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="11" t="n"/>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="14">
+        <f>M53/N53</f>
+        <v/>
+      </c>
+      <c r="M52" s="4">
+        <f>I53-H53</f>
+        <v/>
+      </c>
+      <c r="N52" s="26">
+        <f>F53-E53</f>
+        <v/>
+      </c>
+      <c r="O52" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P52" s="33" t="inlineStr">
+        <is>
+          <t>1396у_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>144</v>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>46127.08333333334</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>46135.08333333334</v>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="n"/>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="12" t="n"/>
+      <c r="L53" s="13">
+        <f>M54/N54</f>
+        <v/>
+      </c>
+      <c r="M53" s="3">
+        <f>I54-H54</f>
+        <v/>
+      </c>
+      <c r="N53" s="27">
+        <f>F54-E54</f>
+        <v/>
+      </c>
+      <c r="O53" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P53" s="32" t="inlineStr">
+        <is>
+          <t>144_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>220(2)</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>46129.08333333334</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>46149.08333333334</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H54" s="11" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="11" t="n"/>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="14">
+        <f>M55/N55</f>
+        <v/>
+      </c>
+      <c r="M54" s="4">
+        <f>I55-H55</f>
+        <v/>
+      </c>
+      <c r="N54" s="26">
+        <f>F55-E55</f>
+        <v/>
+      </c>
+      <c r="O54" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P54" s="33" t="inlineStr">
+        <is>
+          <t>220(2)_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="n">
+        <v>220</v>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
         <v>46137.08333333334</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F55" s="12" t="n">
+        <v>46151.08333333334</v>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="n"/>
+      <c r="I55" s="12" t="n"/>
+      <c r="J55" s="12" t="n"/>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="13">
+        <f>M56/N56</f>
+        <v/>
+      </c>
+      <c r="M55" s="3">
+        <f>I56-H56</f>
+        <v/>
+      </c>
+      <c r="N55" s="27">
+        <f>F56-E56</f>
+        <v/>
+      </c>
+      <c r="O55" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P55" s="32" t="inlineStr">
+        <is>
+          <t>220_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="n">
+        <v>254</v>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>46127.08333333334</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>46147.08333333334</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="11" t="n"/>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="14">
+        <f>M57/N57</f>
+        <v/>
+      </c>
+      <c r="M56" s="4">
+        <f>I57-H57</f>
+        <v/>
+      </c>
+      <c r="N56" s="26">
+        <f>F57-E57</f>
+        <v/>
+      </c>
+      <c r="O56" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P56" s="33" t="inlineStr">
+        <is>
+          <t>254_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>2661</v>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>46125.08333333334</v>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>46133.08333333334</v>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="n"/>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="13">
+        <f>M58/N58</f>
+        <v/>
+      </c>
+      <c r="M57" s="3">
+        <f>I58-H58</f>
+        <v/>
+      </c>
+      <c r="N57" s="27">
+        <f>F58-E58</f>
+        <v/>
+      </c>
+      <c r="O57" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P57" s="32" t="inlineStr">
+        <is>
+          <t>2661_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="n">
+        <v>4649</v>
+      </c>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>46125.08333333334</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="11" t="n"/>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="14">
+        <f>M59/N59</f>
+        <v/>
+      </c>
+      <c r="M58" s="4">
+        <f>I59-H59</f>
+        <v/>
+      </c>
+      <c r="N58" s="26">
+        <f>F59-E59</f>
+        <v/>
+      </c>
+      <c r="O58" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P58" s="33" t="inlineStr">
+        <is>
+          <t>4649_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>512</v>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>46125.08333333334</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="n"/>
+      <c r="I59" s="12" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="12" t="n"/>
+      <c r="L59" s="13">
+        <f>M60/N60</f>
+        <v/>
+      </c>
+      <c r="M59" s="3">
+        <f>I60-H60</f>
+        <v/>
+      </c>
+      <c r="N59" s="27">
+        <f>F60-E60</f>
+        <v/>
+      </c>
+      <c r="O59" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P59" s="32" t="inlineStr">
+        <is>
+          <t>512_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="n">
+        <v>5302</v>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>46127.08333333334</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>46133.08333333334</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="11" t="n"/>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="14">
+        <f>M61/N61</f>
+        <v/>
+      </c>
+      <c r="M60" s="4">
+        <f>I61-H61</f>
+        <v/>
+      </c>
+      <c r="N60" s="26">
+        <f>F61-E61</f>
+        <v/>
+      </c>
+      <c r="O60" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P60" s="33" t="inlineStr">
+        <is>
+          <t>5302_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>5467</v>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>46127.08333333334</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>46151.08333333334</v>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="13">
+        <f>M62/N62</f>
+        <v/>
+      </c>
+      <c r="M61" s="3">
+        <f>I62-H62</f>
+        <v/>
+      </c>
+      <c r="N61" s="27">
+        <f>F62-E62</f>
+        <v/>
+      </c>
+      <c r="O61" s="29" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P61" s="32" t="inlineStr">
+        <is>
+          <t>5467_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C62" s="22" t="n">
+        <v>610</v>
+      </c>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>46125.08333333334</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>46133.08333333334</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>norm_work — чисто нормальная работа</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="11" t="n"/>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="14">
+        <f>M63/N63</f>
+        <v/>
+      </c>
+      <c r="M62" s="4">
+        <f>I63-H63</f>
+        <v/>
+      </c>
+      <c r="N62" s="26">
+        <f>F63-E63</f>
+        <v/>
+      </c>
+      <c r="O62" s="30" t="inlineStr">
+        <is>
+          <t>norm_work</t>
+        </is>
+      </c>
+      <c r="P62" s="33" t="inlineStr">
+        <is>
+          <t>610_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>Южно-Ягунское</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="n">
+        <v>660</v>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>Нормальная работа</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="F63" s="12" t="n">
         <v>46149.08333333334</v>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>norm_work — чисто нормальная работа</t>
         </is>
       </c>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="11" t="n"/>
-      <c r="K47" s="11" t="n"/>
-      <c r="L47" s="14">
-        <f>M47/N47</f>
-        <v/>
-      </c>
-      <c r="M47" s="4">
-        <f>I47-H47</f>
-        <v/>
-      </c>
-      <c r="N47" s="26">
-        <f>F47-E47</f>
-        <v/>
-      </c>
-      <c r="O47" s="30" t="inlineStr">
+      <c r="H63" s="12" t="n"/>
+      <c r="I63" s="12" t="n"/>
+      <c r="J63" s="12" t="n"/>
+      <c r="K63" s="12" t="n"/>
+      <c r="L63" s="13">
+        <f>M64/N64</f>
+        <v/>
+      </c>
+      <c r="M63" s="3">
+        <f>I64-H64</f>
+        <v/>
+      </c>
+      <c r="N63" s="27">
+        <f>F64-E64</f>
+        <v/>
+      </c>
+      <c r="O63" s="29" t="inlineStr">
         <is>
           <t>norm_work</t>
         </is>
       </c>
-      <c r="P47" s="33" t="inlineStr">
-        <is>
-          <t>1151_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
+      <c r="P63" s="32" t="inlineStr">
+        <is>
+          <t>660_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
         <is>
           <t>Южно-Ягунское</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>1213л</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="C64" s="22" t="n">
+        <v>662</v>
+      </c>
+      <c r="D64" s="22" t="inlineStr">
         <is>
           <t>Нормальная работа</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E64" s="11" t="n">
         <v>46125.08333333334</v>
       </c>
-      <c r="F48" s="12" t="n">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="F64" s="11" t="n">
+        <v>46137.08333333334</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
         <is>
           <t>norm_work — чисто нормальная работа</t>
         </is>
       </c>
-      <c r="H48" s="12" t="n"/>
-      <c r="I48" s="12" t="n"/>
-      <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="13">
-        <f>M48/N48</f>
-        <v/>
-      </c>
-      <c r="M48" s="3">
-        <f>I48-H48</f>
-        <v/>
-      </c>
-      <c r="N48" s="27">
-        <f>F48-E48</f>
-        <v/>
-      </c>
-      <c r="O48" s="29" t="inlineStr">
+      <c r="H64" s="11" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="11" t="n"/>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="14">
+        <f>M65/N65</f>
+        <v/>
+      </c>
+      <c r="M64" s="4">
+        <f>I65-H65</f>
+        <v/>
+      </c>
+      <c r="N64" s="26">
+        <f>F65-E65</f>
+        <v/>
+      </c>
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>norm_work</t>
         </is>
       </c>
-      <c r="P48" s="32" t="inlineStr">
-        <is>
-          <t>1213л_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="P64" s="33" t="inlineStr">
+        <is>
+          <t>662_ЮЯ_Нормальная работа.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
         <is>
           <t>Южно-Ягунское</t>
         </is>
       </c>
-      <c r="C49" s="22" t="inlineStr">
-        <is>
-          <t>1214у</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
+      <c r="C65" s="24" t="n">
+        <v>8016</v>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
         <is>
           <t>Нормальная работа</t>
         </is>
       </c>
-      <c r="E49" s="11" t="n">
-        <v>46131.08333333334</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="E65" s="16" t="n">
+        <v>46137.08333333334</v>
+      </c>
+      <c r="F65" s="16" t="n">
+        <v>46151.08333333334</v>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
         <is>
           <t>norm_work — чисто нормальная работа</t>
         </is>
       </c>
-      <c r="H49" s="11" t="n"/>
-      <c r="I49" s="11" t="n"/>
-      <c r="J49" s="11" t="n"/>
-      <c r="K49" s="11" t="n"/>
-      <c r="L49" s="14">
-        <f>M49/N49</f>
-        <v/>
-      </c>
-      <c r="M49" s="4">
-        <f>I49-H49</f>
-        <v/>
-      </c>
-      <c r="N49" s="26">
-        <f>F49-E49</f>
-        <v/>
-      </c>
-      <c r="O49" s="30" t="inlineStr">
+      <c r="H65" s="16" t="n"/>
+      <c r="I65" s="16" t="n"/>
+      <c r="J65" s="16" t="n"/>
+      <c r="K65" s="16" t="n"/>
+      <c r="L65" s="17">
+        <f>M66/N66</f>
+        <v/>
+      </c>
+      <c r="M65" s="21">
+        <f>I66-H66</f>
+        <v/>
+      </c>
+      <c r="N65" s="28">
+        <f>F66-E66</f>
+        <v/>
+      </c>
+      <c r="O65" s="31" t="inlineStr">
         <is>
           <t>norm_work</t>
         </is>
       </c>
-      <c r="P49" s="33" t="inlineStr">
-        <is>
-          <t>1214у_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="n">
-        <v>1247</v>
-      </c>
-      <c r="D50" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>46129.08333333334</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>46149.08333333334</v>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="n"/>
-      <c r="I50" s="12" t="n"/>
-      <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="13">
-        <f>M50/N50</f>
-        <v/>
-      </c>
-      <c r="M50" s="3">
-        <f>I50-H50</f>
-        <v/>
-      </c>
-      <c r="N50" s="27">
-        <f>F50-E50</f>
-        <v/>
-      </c>
-      <c r="O50" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P50" s="32" t="inlineStr">
-        <is>
-          <t>1247_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="n">
-        <v>126</v>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>46129.08333333334</v>
-      </c>
-      <c r="F51" s="11" t="n">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="11" t="n"/>
-      <c r="K51" s="11" t="n"/>
-      <c r="L51" s="14">
-        <f>M51/N51</f>
-        <v/>
-      </c>
-      <c r="M51" s="4">
-        <f>I51-H51</f>
-        <v/>
-      </c>
-      <c r="N51" s="26">
-        <f>F51-E51</f>
-        <v/>
-      </c>
-      <c r="O51" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P51" s="33" t="inlineStr">
-        <is>
-          <t>126_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C52" s="23" t="inlineStr">
-        <is>
-          <t>129л</t>
-        </is>
-      </c>
-      <c r="D52" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>46125.08333333334</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>46149.08333333334</v>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="n"/>
-      <c r="I52" s="12" t="n"/>
-      <c r="J52" s="12" t="n"/>
-      <c r="K52" s="12" t="n"/>
-      <c r="L52" s="13">
-        <f>M52/N52</f>
-        <v/>
-      </c>
-      <c r="M52" s="3">
-        <f>I52-H52</f>
-        <v/>
-      </c>
-      <c r="N52" s="27">
-        <f>F52-E52</f>
-        <v/>
-      </c>
-      <c r="O52" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P52" s="32" t="inlineStr">
-        <is>
-          <t>129л_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="inlineStr">
-        <is>
-          <t>1396у</t>
-        </is>
-      </c>
-      <c r="D53" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="n">
-        <v>46113.08333333334</v>
-      </c>
-      <c r="F53" s="11" t="n">
-        <v>46143.08333333334</v>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="n"/>
-      <c r="I53" s="11" t="n"/>
-      <c r="J53" s="11" t="n"/>
-      <c r="K53" s="11" t="n"/>
-      <c r="L53" s="14">
-        <f>M53/N53</f>
-        <v/>
-      </c>
-      <c r="M53" s="4">
-        <f>I53-H53</f>
-        <v/>
-      </c>
-      <c r="N53" s="26">
-        <f>F53-E53</f>
-        <v/>
-      </c>
-      <c r="O53" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P53" s="33" t="inlineStr">
-        <is>
-          <t>1396у_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="B54" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C54" s="23" t="n">
-        <v>144</v>
-      </c>
-      <c r="D54" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="n">
-        <v>46127.08333333334</v>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>46135.08333333334</v>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="n"/>
-      <c r="I54" s="12" t="n"/>
-      <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="13">
-        <f>M54/N54</f>
-        <v/>
-      </c>
-      <c r="M54" s="3">
-        <f>I54-H54</f>
-        <v/>
-      </c>
-      <c r="N54" s="27">
-        <f>F54-E54</f>
-        <v/>
-      </c>
-      <c r="O54" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P54" s="32" t="inlineStr">
-        <is>
-          <t>144_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B55" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>220(2)</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v>46129.08333333334</v>
-      </c>
-      <c r="F55" s="11" t="n">
-        <v>46149.08333333334</v>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="11" t="n"/>
-      <c r="K55" s="11" t="n"/>
-      <c r="L55" s="14">
-        <f>M55/N55</f>
-        <v/>
-      </c>
-      <c r="M55" s="4">
-        <f>I55-H55</f>
-        <v/>
-      </c>
-      <c r="N55" s="26">
-        <f>F55-E55</f>
-        <v/>
-      </c>
-      <c r="O55" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P55" s="33" t="inlineStr">
-        <is>
-          <t>220(2)_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="B56" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C56" s="23" t="n">
-        <v>220</v>
-      </c>
-      <c r="D56" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="n">
-        <v>46137.08333333334</v>
-      </c>
-      <c r="F56" s="12" t="n">
-        <v>46151.08333333334</v>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="n"/>
-      <c r="I56" s="12" t="n"/>
-      <c r="J56" s="12" t="n"/>
-      <c r="K56" s="12" t="n"/>
-      <c r="L56" s="13">
-        <f>M56/N56</f>
-        <v/>
-      </c>
-      <c r="M56" s="3">
-        <f>I56-H56</f>
-        <v/>
-      </c>
-      <c r="N56" s="27">
-        <f>F56-E56</f>
-        <v/>
-      </c>
-      <c r="O56" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P56" s="32" t="inlineStr">
-        <is>
-          <t>220_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="n">
-        <v>254</v>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>46127.08333333334</v>
-      </c>
-      <c r="F57" s="11" t="n">
-        <v>46147.08333333334</v>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="n"/>
-      <c r="I57" s="11" t="n"/>
-      <c r="J57" s="11" t="n"/>
-      <c r="K57" s="11" t="n"/>
-      <c r="L57" s="14">
-        <f>M57/N57</f>
-        <v/>
-      </c>
-      <c r="M57" s="4">
-        <f>I57-H57</f>
-        <v/>
-      </c>
-      <c r="N57" s="26">
-        <f>F57-E57</f>
-        <v/>
-      </c>
-      <c r="O57" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P57" s="33" t="inlineStr">
-        <is>
-          <t>254_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C58" s="23" t="n">
-        <v>2661</v>
-      </c>
-      <c r="D58" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="n">
-        <v>46125.08333333334</v>
-      </c>
-      <c r="F58" s="12" t="n">
-        <v>46133.08333333334</v>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="n"/>
-      <c r="I58" s="12" t="n"/>
-      <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="13">
-        <f>M58/N58</f>
-        <v/>
-      </c>
-      <c r="M58" s="3">
-        <f>I58-H58</f>
-        <v/>
-      </c>
-      <c r="N58" s="27">
-        <f>F58-E58</f>
-        <v/>
-      </c>
-      <c r="O58" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P58" s="32" t="inlineStr">
-        <is>
-          <t>2661_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C59" s="22" t="n">
-        <v>4649</v>
-      </c>
-      <c r="D59" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>46125.08333333334</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H59" s="11" t="n"/>
-      <c r="I59" s="11" t="n"/>
-      <c r="J59" s="11" t="n"/>
-      <c r="K59" s="11" t="n"/>
-      <c r="L59" s="14">
-        <f>M59/N59</f>
-        <v/>
-      </c>
-      <c r="M59" s="4">
-        <f>I59-H59</f>
-        <v/>
-      </c>
-      <c r="N59" s="26">
-        <f>F59-E59</f>
-        <v/>
-      </c>
-      <c r="O59" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P59" s="33" t="inlineStr">
-        <is>
-          <t>4649_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C60" s="23" t="n">
-        <v>512</v>
-      </c>
-      <c r="D60" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="n">
-        <v>46125.08333333334</v>
-      </c>
-      <c r="F60" s="12" t="n">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H60" s="12" t="n"/>
-      <c r="I60" s="12" t="n"/>
-      <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="13">
-        <f>M60/N60</f>
-        <v/>
-      </c>
-      <c r="M60" s="3">
-        <f>I60-H60</f>
-        <v/>
-      </c>
-      <c r="N60" s="27">
-        <f>F60-E60</f>
-        <v/>
-      </c>
-      <c r="O60" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P60" s="32" t="inlineStr">
-        <is>
-          <t>512_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C61" s="22" t="n">
-        <v>5302</v>
-      </c>
-      <c r="D61" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v>46127.08333333334</v>
-      </c>
-      <c r="F61" s="11" t="n">
-        <v>46133.08333333334</v>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H61" s="11" t="n"/>
-      <c r="I61" s="11" t="n"/>
-      <c r="J61" s="11" t="n"/>
-      <c r="K61" s="11" t="n"/>
-      <c r="L61" s="14">
-        <f>M61/N61</f>
-        <v/>
-      </c>
-      <c r="M61" s="4">
-        <f>I61-H61</f>
-        <v/>
-      </c>
-      <c r="N61" s="26">
-        <f>F61-E61</f>
-        <v/>
-      </c>
-      <c r="O61" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P61" s="33" t="inlineStr">
-        <is>
-          <t>5302_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="B62" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C62" s="23" t="n">
-        <v>5467</v>
-      </c>
-      <c r="D62" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="n">
-        <v>46127.08333333334</v>
-      </c>
-      <c r="F62" s="12" t="n">
-        <v>46151.08333333334</v>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H62" s="12" t="n"/>
-      <c r="I62" s="12" t="n"/>
-      <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="13">
-        <f>M62/N62</f>
-        <v/>
-      </c>
-      <c r="M62" s="3">
-        <f>I62-H62</f>
-        <v/>
-      </c>
-      <c r="N62" s="27">
-        <f>F62-E62</f>
-        <v/>
-      </c>
-      <c r="O62" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P62" s="32" t="inlineStr">
-        <is>
-          <t>5467_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B63" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C63" s="22" t="n">
-        <v>610</v>
-      </c>
-      <c r="D63" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v>46125.08333333334</v>
-      </c>
-      <c r="F63" s="11" t="n">
-        <v>46133.08333333334</v>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H63" s="11" t="n"/>
-      <c r="I63" s="11" t="n"/>
-      <c r="J63" s="11" t="n"/>
-      <c r="K63" s="11" t="n"/>
-      <c r="L63" s="14">
-        <f>M63/N63</f>
-        <v/>
-      </c>
-      <c r="M63" s="4">
-        <f>I63-H63</f>
-        <v/>
-      </c>
-      <c r="N63" s="26">
-        <f>F63-E63</f>
-        <v/>
-      </c>
-      <c r="O63" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P63" s="33" t="inlineStr">
-        <is>
-          <t>610_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="B64" s="23" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C64" s="23" t="n">
-        <v>660</v>
-      </c>
-      <c r="D64" s="23" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="n">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="F64" s="12" t="n">
-        <v>46149.08333333334</v>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="n"/>
-      <c r="I64" s="12" t="n"/>
-      <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="13">
-        <f>M64/N64</f>
-        <v/>
-      </c>
-      <c r="M64" s="3">
-        <f>I64-H64</f>
-        <v/>
-      </c>
-      <c r="N64" s="27">
-        <f>F64-E64</f>
-        <v/>
-      </c>
-      <c r="O64" s="29" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P64" s="32" t="inlineStr">
-        <is>
-          <t>660_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C65" s="22" t="n">
-        <v>662</v>
-      </c>
-      <c r="D65" s="22" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v>46125.08333333334</v>
-      </c>
-      <c r="F65" s="11" t="n">
-        <v>46137.08333333334</v>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="n"/>
-      <c r="I65" s="11" t="n"/>
-      <c r="J65" s="11" t="n"/>
-      <c r="K65" s="11" t="n"/>
-      <c r="L65" s="14">
-        <f>M65/N65</f>
-        <v/>
-      </c>
-      <c r="M65" s="4">
-        <f>I65-H65</f>
-        <v/>
-      </c>
-      <c r="N65" s="26">
-        <f>F65-E65</f>
-        <v/>
-      </c>
-      <c r="O65" s="30" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P65" s="33" t="inlineStr">
-        <is>
-          <t>662_ЮЯ_Нормальная работа.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" thickBot="1">
-      <c r="A66" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>Южно-Ягунское</t>
-        </is>
-      </c>
-      <c r="C66" s="24" t="n">
-        <v>8016</v>
-      </c>
-      <c r="D66" s="24" t="inlineStr">
-        <is>
-          <t>Нормальная работа</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>46137.08333333334</v>
-      </c>
-      <c r="F66" s="16" t="n">
-        <v>46151.08333333334</v>
-      </c>
-      <c r="G66" s="18" t="inlineStr">
-        <is>
-          <t>norm_work — чисто нормальная работа</t>
-        </is>
-      </c>
-      <c r="H66" s="16" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="16" t="n"/>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="17">
-        <f>M66/N66</f>
-        <v/>
-      </c>
-      <c r="M66" s="21">
-        <f>I66-H66</f>
-        <v/>
-      </c>
-      <c r="N66" s="28">
-        <f>F66-E66</f>
-        <v/>
-      </c>
-      <c r="O66" s="31" t="inlineStr">
-        <is>
-          <t>norm_work</t>
-        </is>
-      </c>
-      <c r="P66" s="34" t="inlineStr">
+      <c r="P65" s="34" t="inlineStr">
         <is>
           <t>8016_ЮЯ_Нормальная работа.xlsx</t>
         </is>
       </c>
     </row>
+    <row r="66" ht="15" customHeight="1" thickBot="1"/>
     <row r="74" ht="15" customHeight="1"/>
     <row r="94" ht="15" customHeight="1"/>
   </sheetData>
